--- a/JsonConverter/ExcelFiles/UnitData.xlsx
+++ b/JsonConverter/ExcelFiles/UnitData.xlsx
@@ -744,7 +744,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="9" t="n">
-        <v>1</v>
+        <v>0.06</v>
       </c>
       <c r="G4" s="9" t="n">
         <v>1</v>
@@ -784,7 +784,7 @@
         <v>1.5</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>5</v>
+        <v>0.2</v>
       </c>
       <c r="G5" s="9" t="n">
         <v>1</v>
@@ -864,7 +864,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="9" t="n">
-        <v>3</v>
+        <v>0.15</v>
       </c>
       <c r="G7" s="9" t="n">
         <v>0</v>
